--- a/Configs/GameConfig/Datas/HeroConfig.xlsx
+++ b/Configs/GameConfig/Datas/HeroConfig.xlsx
@@ -2,39 +2,368 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="25600" windowHeight="12080" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
+  <fonts count="20">
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -42,15 +371,305 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -403,7 +1022,6 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -413,8 +1031,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:AI6"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="5"/>
+  <cols>
+    <col width="8.54545454545454" customWidth="1" min="1" max="1"/>
+    <col width="7.54545454545455" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="7.54545454545455" customWidth="1" min="4" max="4"/>
+    <col width="9.54545454545454" customWidth="1" min="5" max="5"/>
+    <col width="17.3636363636364" customWidth="1" min="6" max="8"/>
+    <col width="10.6363636363636" customWidth="1" min="9" max="9"/>
+    <col width="8.54545454545454" customWidth="1" min="10" max="10"/>
+    <col width="9.54545454545454" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="16"/>
+    <col width="5.54545454545455" customWidth="1" min="17" max="18"/>
+    <col width="6.54545454545455" customWidth="1" min="19" max="19"/>
+    <col width="18.5454545454545" customWidth="1" min="20" max="20"/>
+    <col width="11.8181818181818" customWidth="1" min="21" max="22"/>
+    <col width="18.5454545454545" customWidth="1" min="23" max="24"/>
+    <col width="29.8181818181818" customWidth="1" min="25" max="25"/>
+    <col width="9.54545454545454" customWidth="1" min="26" max="27"/>
+    <col width="36.5454545454545" customWidth="1" min="28" max="28"/>
+    <col width="46.6363636363636" customWidth="1" min="29" max="29"/>
+    <col width="36.5454545454545" customWidth="1" min="30" max="32"/>
+    <col width="42.1818181818182" customWidth="1" min="33" max="33"/>
+    <col width="28.6363636363636" customWidth="1" min="34" max="34"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -554,17 +1196,37 @@
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>MoveSpeed</t>
+          <t>WalkSpeed</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
+          <t>RunSpeed</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>RunDoubleTapWindow</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>IdleEmoteDelay</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
           <t>JumpSpeed</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Gravity</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>JumpCountMax</t>
         </is>
       </c>
     </row>
@@ -726,6 +1388,26 @@
           <t>float</t>
         </is>
       </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>vector2</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -872,17 +1554,37 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>移动速度 px/s(旧 walk_speed=240)</t>
+          <t>慢走速度 px/s</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
+          <t>跑步(快走)速度 px/s</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>双击方向键进入跑步的判定窗口(秒)</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>待机后隔多久随机播一次憨笑(秒,x=最短,y=最长)</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
           <t>起跳速度(向上为正,旧 jump_power=-540)</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>重力(旧 gravity=980 向下)</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>最多跳跃次数(含地面一段与空中段,旧 jump_count&lt;2 判据)</t>
         </is>
       </c>
     </row>
@@ -972,13 +1674,27 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
+        <v>120</v>
+      </c>
+      <c r="AC6" t="n">
         <v>240</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AD6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>6,12</t>
+        </is>
+      </c>
+      <c r="AF6" t="n">
         <v>540</v>
       </c>
-      <c r="AD6" t="n">
+      <c r="AG6" t="n">
         <v>980</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/HeroConfig.xlsx
+++ b/Configs/GameConfig/Datas/HeroConfig.xlsx
@@ -1031,7 +1031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI6"/>
+  <dimension ref="A1:AJ6"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="5"/>
   <cols>
     <col width="8.54545454545454" customWidth="1" min="1" max="1"/>
@@ -1056,6 +1056,7 @@
     <col width="36.5454545454545" customWidth="1" min="30" max="32"/>
     <col width="42.1818181818182" customWidth="1" min="33" max="33"/>
     <col width="28.6363636363636" customWidth="1" min="34" max="34"/>
+    <col width="33.1818181818182" customWidth="1" min="35" max="36"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1224,9 +1225,19 @@
           <t>Gravity</t>
         </is>
       </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>JumpCountMax</t>
+        </is>
+      </c>
       <c r="AI1" t="inlineStr">
         <is>
-          <t>JumpCountMax</t>
+          <t>HurtSoundId</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>DeathSoundId</t>
         </is>
       </c>
     </row>
@@ -1403,9 +1414,19 @@
           <t>float</t>
         </is>
       </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>Sound.SoundId</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>Sound.SoundId</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1590,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>待机后隔多久随机播一次憨笑(秒,x=最短,y=最长)</t>
+          <t>待机后隔多久随机播一次憨笑(秒,x=最短,y=最长,写法 6,12)</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -1582,9 +1603,19 @@
           <t>重力(旧 gravity=980 向下)</t>
         </is>
       </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>最多跳跃次数(含地面一段与空中段,旧 jump_count&lt;2 判据)</t>
+        </is>
+      </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>最多跳跃次数(含地面一段与空中段,旧 jump_count&lt;2 判据)</t>
+          <t>受击语音(自己挨打时的声音,None=无;按受害者选音,BaseHero.gd:592)</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>死亡语音(None=无)</t>
         </is>
       </c>
     </row>
@@ -1693,8 +1724,18 @@
       <c r="AG6" t="n">
         <v>980</v>
       </c>
-      <c r="AI6" t="n">
+      <c r="AH6" t="n">
         <v>2</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>WukongHurt</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>WukongDeath</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/HeroConfig.xlsx
+++ b/Configs/GameConfig/Datas/HeroConfig.xlsx
@@ -1031,7 +1031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ6"/>
+  <dimension ref="A1:AK6"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="5"/>
   <cols>
     <col width="8.54545454545454" customWidth="1" min="1" max="1"/>
@@ -1240,6 +1240,11 @@
           <t>DeathSoundId</t>
         </is>
       </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>InputBufferTime</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1429,6 +1434,11 @@
           <t>Sound.SoundId</t>
         </is>
       </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1616,6 +1626,11 @@
       <c r="AJ5" t="inlineStr">
         <is>
           <t>死亡语音(None=无)</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>输入缓冲秒:跳跃/普攻按键在这段时间内等到可执行时机仍生效(0=只在按下那一帧有效)</t>
         </is>
       </c>
     </row>
@@ -1736,6 +1751,9 @@
         <is>
           <t>WukongDeath</t>
         </is>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/HeroConfig.xlsx
+++ b/Configs/GameConfig/Datas/HeroConfig.xlsx
@@ -1092,155 +1092,50 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>BaseHp</t>
+          <t>WalkSpeed</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>BaseMp</t>
+          <t>RunSpeed</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>BasePower</t>
+          <t>RunDoubleTapWindow</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>BaseDef</t>
+          <t>IdleEmoteDelay</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>BaseMdef</t>
+          <t>JumpSpeed</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>GrowHp</t>
+          <t>Gravity</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>GrowMp</t>
+          <t>JumpCountMax</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>GrowPower</t>
+          <t>HurtSoundId</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>GrowDef</t>
+          <t>DeathSoundId</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
-        <is>
-          <t>GrowMdef</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>Crit</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>Miss</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>Lucky</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>Toughness</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Htarget</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>CritReduce</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>Ar</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>Sp</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>Vampirism</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>RHp</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>RMp</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>WalkSpeed</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>RunSpeed</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>RunDoubleTapWindow</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>IdleEmoteDelay</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>JumpSpeed</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>Gravity</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>JumpCountMax</t>
-        </is>
-      </c>
-      <c r="AI1" t="inlineStr">
-        <is>
-          <t>HurtSoundId</t>
-        </is>
-      </c>
-      <c r="AJ1" t="inlineStr">
-        <is>
-          <t>DeathSoundId</t>
-        </is>
-      </c>
-      <c r="AK1" t="inlineStr">
         <is>
           <t>InputBufferTime</t>
         </is>
@@ -1286,155 +1181,50 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>vector2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
           <t>int</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>Sound.SoundId</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>Sound.SoundId</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>vector2</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Sound.SoundId</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>Sound.SoundId</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
         <is>
           <t>float</t>
         </is>
@@ -1480,155 +1270,50 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1级生命(旧 SHp)</t>
+          <t>慢走速度 px/s</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1级魔法(旧 SMp)</t>
+          <t>跑步(快走)速度 px/s</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1级攻击</t>
+          <t>双击方向键进入跑步的判定窗口(秒)</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1级物防</t>
+          <t>待机后隔多久随机播一次憨笑(秒,x=最短,y=最长,写法 6,12)</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1级魔防</t>
+          <t>起跳速度(向上为正,旧 jump_power=-540)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>每级生命成长</t>
+          <t>重力(旧 gravity=980 向下)</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>每级魔法成长</t>
+          <t>最多跳跃次数(含地面一段与空中段,旧 jump_count&lt;2 判据)</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>每级攻击成长</t>
+          <t>受击语音(自己挨打时的声音,None=无;按受害者选音,BaseHero.gd:592)</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>每级物防成长</t>
+          <t>死亡语音(None=无)</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
-        <is>
-          <t>每级魔防成长</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>暴击</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>闪避</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>幸运</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>韧性(减对方幸运)</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>命中(破闪)</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>暴击抵抗</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>破甲(减对方物防)</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>破魔(减对方魔防)</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>吸血系数(物理伤害转化回血)</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>每秒回血</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>每秒回魔</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>慢走速度 px/s</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>跑步(快走)速度 px/s</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>双击方向键进入跑步的判定窗口(秒)</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>待机后隔多久随机播一次憨笑(秒,x=最短,y=最长,写法 6,12)</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>起跳速度(向上为正,旧 jump_power=-540)</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>重力(旧 gravity=980 向下)</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>最多跳跃次数(含地面一段与空中段,旧 jump_count&lt;2 判据)</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>受击语音(自己挨打时的声音,None=无;按受害者选音,BaseHero.gd:592)</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>死亡语音(None=无)</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
         <is>
           <t>输入缓冲秒:跳跃/普攻按键在这段时间内等到可执行时机仍生效(0=只在按下那一帧有效)</t>
         </is>
@@ -1657,102 +1342,39 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="H6" t="n">
-        <v>50</v>
+        <v>240</v>
       </c>
       <c r="I6" t="n">
-        <v>8</v>
-      </c>
-      <c r="J6" t="n">
-        <v>10</v>
+        <v>0.3</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>6,12</t>
+        </is>
       </c>
       <c r="K6" t="n">
-        <v>10</v>
+        <v>540</v>
       </c>
       <c r="L6" t="n">
-        <v>50</v>
+        <v>980</v>
       </c>
       <c r="M6" t="n">
-        <v>15</v>
-      </c>
-      <c r="N6" t="n">
-        <v>4</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>WukongHurt</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>WukongDeath</t>
+        </is>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>120</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>240</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>6,12</t>
-        </is>
-      </c>
-      <c r="AF6" t="n">
-        <v>540</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>980</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>WukongHurt</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>WukongDeath</t>
-        </is>
-      </c>
-      <c r="AK6" t="n">
         <v>0.1</v>
       </c>
     </row>

--- a/Configs/GameConfig/Datas/HeroConfig.xlsx
+++ b/Configs/GameConfig/Datas/HeroConfig.xlsx
@@ -1,177 +1,154 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="25600" windowHeight="12080" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R714fa3b69f944931"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <fonts count="20">
     <font>
-      <name val="宋体"/>
-      <charset val="134"/>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u val="single"/>
+      <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <sz val="11"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <sz val="11"/>
       <color rgb="FF800080"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
       <color theme="3"/>
-      <sz val="18"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <i val="1"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
       <color theme="3"/>
-      <sz val="15"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
       <color theme="3"/>
-      <sz val="13"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="3"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF006100"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <name val="宋体"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -179,187 +156,156 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39998"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39998"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39998"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39998"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39998"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39998"/>
       </patternFill>
     </fill>
   </fills>
@@ -400,7 +346,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4" tint="0.49998"/>
       </bottom>
       <diagonal/>
     </border>
@@ -617,61 +563,63 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规" xfId="0"/>
+    <cellStyle name="千位分隔" xfId="1"/>
+    <cellStyle name="货币" xfId="2"/>
+    <cellStyle name="百分比" xfId="3"/>
+    <cellStyle name="千位分隔[0]" xfId="4"/>
+    <cellStyle name="货币[0]" xfId="5"/>
+    <cellStyle name="超链接" xfId="6"/>
+    <cellStyle name="已访问的超链接" xfId="7"/>
+    <cellStyle name="注释" xfId="8"/>
+    <cellStyle name="警告文本" xfId="9"/>
+    <cellStyle name="标题" xfId="10"/>
+    <cellStyle name="解释性文本" xfId="11"/>
+    <cellStyle name="标题 1" xfId="12"/>
+    <cellStyle name="标题 2" xfId="13"/>
+    <cellStyle name="标题 3" xfId="14"/>
+    <cellStyle name="标题 4" xfId="15"/>
+    <cellStyle name="输入" xfId="16"/>
+    <cellStyle name="输出" xfId="17"/>
+    <cellStyle name="计算" xfId="18"/>
+    <cellStyle name="检查单元格" xfId="19"/>
+    <cellStyle name="链接单元格" xfId="20"/>
+    <cellStyle name="汇总" xfId="21"/>
+    <cellStyle name="好" xfId="22"/>
+    <cellStyle name="差" xfId="23"/>
+    <cellStyle name="适中" xfId="24"/>
+    <cellStyle name="强调文字颜色 1" xfId="25"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28"/>
+    <cellStyle name="强调文字颜色 2" xfId="29"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32"/>
+    <cellStyle name="强调文字颜色 3" xfId="33"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36"/>
+    <cellStyle name="强调文字颜色 4" xfId="37"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40"/>
+    <cellStyle name="强调文字颜色 5" xfId="41"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44"/>
+    <cellStyle name="强调文字颜色 6" xfId="45"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -907,7 +855,7 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -916,13 +864,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -956,17 +904,6 @@
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -1021,305 +958,328 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AK6"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col width="8.54545454545454" customWidth="1" min="1" max="1"/>
-    <col width="7.54545454545455" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="7.54545454545455" customWidth="1" min="4" max="4"/>
-    <col width="9.54545454545454" customWidth="1" min="5" max="5"/>
-    <col width="17.3636363636364" customWidth="1" min="6" max="8"/>
-    <col width="10.6363636363636" customWidth="1" min="9" max="9"/>
-    <col width="8.54545454545454" customWidth="1" min="10" max="10"/>
-    <col width="9.54545454545454" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="16"/>
-    <col width="5.54545454545455" customWidth="1" min="17" max="18"/>
-    <col width="6.54545454545455" customWidth="1" min="19" max="19"/>
-    <col width="18.5454545454545" customWidth="1" min="20" max="20"/>
-    <col width="11.8181818181818" customWidth="1" min="21" max="22"/>
-    <col width="18.5454545454545" customWidth="1" min="23" max="24"/>
-    <col width="29.8181818181818" customWidth="1" min="25" max="25"/>
-    <col width="9.54545454545454" customWidth="1" min="26" max="27"/>
-    <col width="36.5454545454545" customWidth="1" min="28" max="28"/>
-    <col width="46.6363636363636" customWidth="1" min="29" max="29"/>
-    <col width="36.5454545454545" customWidth="1" min="30" max="32"/>
-    <col width="42.1818181818182" customWidth="1" min="33" max="33"/>
-    <col width="28.6363636363636" customWidth="1" min="34" max="34"/>
-    <col width="33.1818181818182" customWidth="1" min="35" max="36"/>
+    <col min="1" max="1" width="8.545454978942871" customWidth="1"/>
+    <col min="2" max="2" width="7.545454502105713" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="7.545454502105713" customWidth="1"/>
+    <col min="5" max="5" width="9.545454978942871" customWidth="1"/>
+    <col min="6" max="8" width="17.363636016845703" customWidth="1"/>
+    <col min="9" max="9" width="24" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="24" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="24" hidden="0" customWidth="1"/>
+    <col min="12" max="16" width="14" customWidth="1"/>
+    <col min="17" max="18" width="5.545454502105713" customWidth="1"/>
+    <col min="19" max="19" width="6.545454502105713" customWidth="1"/>
+    <col min="20" max="20" width="18.545454025268555" customWidth="1"/>
+    <col min="21" max="22" width="11.818181991577148" customWidth="1"/>
+    <col min="23" max="24" width="18.545454025268555" customWidth="1"/>
+    <col min="25" max="25" width="29.81818199157715" customWidth="1"/>
+    <col min="26" max="27" width="9.545454978942871" customWidth="1"/>
+    <col min="28" max="28" width="36.54545593261719" customWidth="1"/>
+    <col min="29" max="29" width="46.6363639831543" customWidth="1"/>
+    <col min="30" max="32" width="36.54545593261719" customWidth="1"/>
+    <col min="33" max="33" width="42.181819915771484" customWidth="1"/>
+    <col min="34" max="34" width="28.636363983154297" customWidth="1"/>
+    <col min="35" max="36" width="33.181819915771484" customWidth="1"/>
+    <col min="7" max="7" width="24" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="24" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="24" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="24" hidden="0" customWidth="1"/>
+    <col min="14" max="14" width="24" hidden="0" customWidth="1"/>
+    <col min="15" max="15" width="55" hidden="0" customWidth="1"/>
+    <col min="16" max="16" width="24" hidden="0" customWidth="1"/>
+    <col min="17" max="17" width="24" hidden="0" customWidth="1"/>
+    <col min="18" max="18" width="24" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="36" customHeight="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>##var</t>
+          <t xml:space="preserve">##var</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Id</t>
+          <t xml:space="preserve">Id</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>LegacyId</t>
+          <t xml:space="preserve">LegacyId</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>NameCn</t>
+          <t xml:space="preserve">NameCn</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Desc</t>
+          <t xml:space="preserve">Desc</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>EntityId</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>WalkSpeed</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>RunSpeed</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>RunDoubleTapWindow</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>IdleEmoteDelay</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>JumpSpeed</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Gravity</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>JumpCountMax</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>HurtSoundId</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>DeathSoundId</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>InputBufferTime</t>
-        </is>
+          <t xml:space="preserve">EntityId</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WalkSpeed</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RunSpeed</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RunDoubleTapWindow</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JumpSpeed</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gravity</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JumpCountMax</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HurtSoundId</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DeathSoundId</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="str">
+        <v>AttackInputCooldowns</v>
+      </c>
+      <c r="P1" s="1" t="str">
+        <v>AirAttackCooldown</v>
+      </c>
+      <c r="Q1" s="1" t="str">
+        <v>ComboResetTime</v>
+      </c>
+      <c r="R1" s="1" t="str">
+        <v>PlatformDropDistance</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>##var</t>
-        </is>
-      </c>
+          <t xml:space="preserve">##var</t>
+        </is>
+      </c>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>##type</t>
+          <t xml:space="preserve">##type</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>int</t>
+          <t xml:space="preserve">int</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>int</t>
+          <t xml:space="preserve">int</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t xml:space="preserve">string</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t xml:space="preserve">string</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Entity.EntityId</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>vector2</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Sound.SoundId</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>Sound.SoundId</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
+          <t xml:space="preserve">Entity.EntityId</t>
+        </is>
+      </c>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">float</t>
+        </is>
+      </c>
+      <c r="H3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">float</t>
+        </is>
+      </c>
+      <c r="I3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">float</t>
+        </is>
+      </c>
+      <c r="J3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">float</t>
+        </is>
+      </c>
+      <c r="K3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">float</t>
+        </is>
+      </c>
+      <c r="L3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">int</t>
+        </is>
+      </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sound.SoundId</t>
+        </is>
+      </c>
+      <c r="N3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sound.SoundId</t>
+        </is>
+      </c>
+      <c r="O3" s="1" t="str">
+        <v>(array#sep=,),float</v>
+      </c>
+      <c r="P3" s="1" t="str">
+        <v>float</v>
+      </c>
+      <c r="Q3" s="1" t="str">
+        <v>float</v>
+      </c>
+      <c r="R3" s="1" t="str">
+        <v>float</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>##group</t>
-        </is>
-      </c>
+          <t xml:space="preserve">##group</t>
+        </is>
+      </c>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1"/>
+      <c r="Q4" s="1"/>
+      <c r="R4" s="1"/>
     </row>
-    <row r="5">
+    <row r="5" ht="85" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>##</t>
+          <t xml:space="preserve">##</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>英雄ID</t>
+          <t xml:space="preserve">英雄ID</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>旧 role 编号</t>
+          <t xml:space="preserve">旧 role 编号</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>中文名</t>
+          <t xml:space="preserve">中文名</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>描述</t>
+          <t xml:space="preserve">描述</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>实体枚举</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>慢走速度 px/s</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>跑步(快走)速度 px/s</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>双击方向键进入跑步的判定窗口(秒)</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>待机后隔多久随机播一次憨笑(秒,x=最短,y=最长,写法 6,12)</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>起跳速度(向上为正,旧 jump_power=-540)</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>重力(旧 gravity=980 向下)</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>最多跳跃次数(含地面一段与空中段,旧 jump_count&lt;2 判据)</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>受击语音(自己挨打时的声音,None=无;按受害者选音,BaseHero.gd:592)</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>死亡语音(None=无)</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>输入缓冲秒:跳跃/普攻按键在这段时间内等到可执行时机仍生效(0=只在按下那一帧有效)</t>
-        </is>
+          <t xml:space="preserve">实体枚举</t>
+        </is>
+      </c>
+      <c r="G5" s="1" t="str">
+        <v>慢走速度px/s，造一悟空6px/帧×24</v>
+      </c>
+      <c r="H5" s="1" t="str">
+        <v>奔跑速度px/s，造一10px/帧×24</v>
+      </c>
+      <c r="I5" s="1" t="str">
+        <v>同方向两次按下间隔严格小于此秒数进入奔跑；原500ms</v>
+      </c>
+      <c r="J5" s="1" t="str">
+        <v>起跳速度px/s，向上为正；造一20px/帧×24</v>
+      </c>
+      <c r="K5" s="1" t="str">
+        <v>重力px/s²，造一1.5px/帧²×24²</v>
+      </c>
+      <c r="L5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最多跳跃次数(含地面一段与空中段,旧 jump_count&lt;2 判据)</t>
+        </is>
+      </c>
+      <c r="M5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">受击语音(自己挨打时的声音,None=无;按受害者选音,BaseHero.gd:592)</t>
+        </is>
+      </c>
+      <c r="N5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">死亡语音(None=无)</t>
+        </is>
+      </c>
+      <c r="O5" s="1" t="str">
+        <v>按上次地面普攻1~5段取本次起手后的冷却秒数，先取值再推进段号；Role1.normalHit 原8/8/15/18/8帧除24</v>
+      </c>
+      <c r="P5" s="1" t="str">
+        <v>空中普攻起手后冷却秒数；原15帧除24</v>
+      </c>
+      <c r="Q5" s="1" t="str">
+        <v>两次普攻尝试间隔超过此秒数重置首段，拒绝的输入也更新时间</v>
+      </c>
+      <c r="R5" s="1" t="str">
+        <v>S+K从单向平台向下移动距离px；普通地面无效</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="30" customHeight="1">
       <c r="B6" t="n">
         <v>1</v>
       </c>
@@ -1328,57 +1288,61 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>悟空</t>
+          <t xml:space="preserve">悟空</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>齐天大圣</t>
+          <t xml:space="preserve">齐天大圣</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Wukong</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>120</v>
-      </c>
-      <c r="H6" t="n">
+          <t xml:space="preserve">Wukong</t>
+        </is>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>144</v>
+      </c>
+      <c r="H6" s="1" t="n">
         <v>240</v>
       </c>
-      <c r="I6" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>6,12</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>540</v>
-      </c>
-      <c r="L6" t="n">
-        <v>980</v>
-      </c>
-      <c r="M6" t="n">
+      <c r="I6" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J6" s="1" t="n">
+        <v>480</v>
+      </c>
+      <c r="K6" s="1" t="n">
+        <v>864</v>
+      </c>
+      <c r="L6" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>WukongHurt</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>WukongDeath</t>
-        </is>
-      </c>
-      <c r="P6" t="n">
-        <v>0.1</v>
+      <c r="M6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WukongHurt</t>
+        </is>
+      </c>
+      <c r="N6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WukongDeath</t>
+        </is>
+      </c>
+      <c r="O6" s="1" t="str">
+        <v>0.333333333,0.333333333,0.625,0.75,0.333333333</v>
+      </c>
+      <c r="P6" s="1" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="Q6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" s="1" t="n">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>